--- a/Excel025-div-rank.xlsx
+++ b/Excel025-div-rank.xlsx
@@ -501,25 +501,25 @@
         <v>534750</v>
       </c>
       <c r="E2" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="F2" t="n">
-        <v>448500</v>
+        <v>441600</v>
       </c>
       <c r="G2" t="n">
         <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>10.38</v>
+        <v>10.1</v>
       </c>
       <c r="I2" t="n">
-        <v>12.37</v>
+        <v>12.22</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>55496.7</v>
+        <v>53985.6</v>
       </c>
     </row>
     <row r="3">
@@ -538,10 +538,10 @@
         <v>571500</v>
       </c>
       <c r="E3" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>409500</v>
+        <v>414000</v>
       </c>
       <c r="G3" t="n">
         <v>4</v>
@@ -550,7 +550,7 @@
         <v>7</v>
       </c>
       <c r="I3" t="n">
-        <v>9.77</v>
+        <v>9.66</v>
       </c>
       <c r="J3" t="n">
         <v>2</v>
@@ -562,251 +562,251 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>WHAIR</t>
+          <t>MCS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="C4" t="n">
-        <v>8.699999999999999</v>
+        <v>15.312</v>
       </c>
       <c r="D4" t="n">
-        <v>435000</v>
+        <v>1148400</v>
       </c>
       <c r="E4" t="n">
-        <v>6.05</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>302500</v>
+        <v>615000</v>
       </c>
       <c r="G4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>6.28</v>
+        <v>4.9</v>
       </c>
       <c r="I4" t="n">
-        <v>9.029999999999999</v>
+        <v>9.15</v>
       </c>
       <c r="J4" t="n">
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>27305</v>
+        <v>56250</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MCS</t>
+          <t>NER</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>75000</v>
+        <v>27000</v>
       </c>
       <c r="C5" t="n">
-        <v>15.312</v>
+        <v>7.45</v>
       </c>
       <c r="D5" t="n">
-        <v>1148400</v>
+        <v>201150</v>
       </c>
       <c r="E5" t="n">
-        <v>8.4</v>
+        <v>4.32</v>
       </c>
       <c r="F5" t="n">
-        <v>630000</v>
+        <v>116640</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H5" t="n">
-        <v>4.9</v>
+        <v>4.83</v>
       </c>
       <c r="I5" t="n">
-        <v>8.93</v>
+        <v>8.33</v>
       </c>
       <c r="J5" t="n">
         <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>56250</v>
+        <v>9720</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NER</t>
+          <t>AIMIRT</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27000</v>
+        <v>17500</v>
       </c>
       <c r="C6" t="n">
-        <v>7.45</v>
+        <v>10.6</v>
       </c>
       <c r="D6" t="n">
-        <v>201150</v>
+        <v>185500</v>
       </c>
       <c r="E6" t="n">
-        <v>4.3</v>
+        <v>10.4</v>
       </c>
       <c r="F6" t="n">
-        <v>116100</v>
+        <v>182000</v>
       </c>
       <c r="G6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H6" t="n">
-        <v>4.83</v>
+        <v>7.92</v>
       </c>
       <c r="I6" t="n">
-        <v>8.369999999999999</v>
+        <v>8.08</v>
       </c>
       <c r="J6" t="n">
         <v>5</v>
       </c>
       <c r="K6" t="n">
-        <v>9720</v>
+        <v>14700</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AIMIRT</t>
+          <t>TFFIF</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17500</v>
+        <v>20000</v>
       </c>
       <c r="C7" t="n">
-        <v>10.6</v>
+        <v>7.2</v>
       </c>
       <c r="D7" t="n">
-        <v>185500</v>
+        <v>144000</v>
       </c>
       <c r="E7" t="n">
-        <v>10.3</v>
+        <v>6.2</v>
       </c>
       <c r="F7" t="n">
-        <v>180250</v>
+        <v>124000</v>
       </c>
       <c r="G7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H7" t="n">
-        <v>8.02</v>
+        <v>6.43</v>
       </c>
       <c r="I7" t="n">
-        <v>8.25</v>
+        <v>7.47</v>
       </c>
       <c r="J7" t="n">
         <v>6</v>
       </c>
       <c r="K7" t="n">
-        <v>14875</v>
+        <v>9266</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TFFIF</t>
+          <t>WHAIR</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20000</v>
+        <v>50000</v>
       </c>
       <c r="C8" t="n">
-        <v>7.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>144000</v>
+        <v>435000</v>
       </c>
       <c r="E8" t="n">
         <v>6.15</v>
       </c>
       <c r="F8" t="n">
-        <v>123000</v>
+        <v>307500</v>
       </c>
       <c r="G8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>6.29</v>
+        <v>5.24</v>
       </c>
       <c r="I8" t="n">
-        <v>7.37</v>
+        <v>7.41</v>
       </c>
       <c r="J8" t="n">
         <v>7</v>
       </c>
       <c r="K8" t="n">
-        <v>9064</v>
+        <v>22785</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>WHART</t>
+          <t>PTT</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>20000</v>
+        <v>7500</v>
       </c>
       <c r="C9" t="n">
-        <v>12.3</v>
+        <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>246000</v>
+        <v>240000</v>
       </c>
       <c r="E9" t="n">
-        <v>9.699999999999999</v>
+        <v>30.75</v>
       </c>
       <c r="F9" t="n">
-        <v>194000</v>
+        <v>230625</v>
       </c>
       <c r="G9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H9" t="n">
-        <v>5.63</v>
+        <v>6.88</v>
       </c>
       <c r="I9" t="n">
-        <v>7.13</v>
+        <v>7.15</v>
       </c>
       <c r="J9" t="n">
         <v>8</v>
       </c>
       <c r="K9" t="n">
-        <v>13840</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CPNREIT</t>
+          <t>WHART</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>55000</v>
+        <v>20000</v>
       </c>
       <c r="C10" t="n">
-        <v>18</v>
+        <v>12.3</v>
       </c>
       <c r="D10" t="n">
-        <v>990000</v>
+        <v>246000</v>
       </c>
       <c r="E10" t="n">
-        <v>11.4</v>
+        <v>9.9</v>
       </c>
       <c r="F10" t="n">
-        <v>627000</v>
+        <v>198000</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H10" t="n">
-        <v>4.43</v>
+        <v>5.63</v>
       </c>
       <c r="I10" t="n">
         <v>6.99</v>
@@ -815,81 +815,81 @@
         <v>9</v>
       </c>
       <c r="K10" t="n">
-        <v>43813</v>
+        <v>13840</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PTT</t>
+          <t>SENA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7500</v>
+        <v>105000</v>
       </c>
       <c r="C11" t="n">
-        <v>32</v>
+        <v>4.48</v>
       </c>
       <c r="D11" t="n">
-        <v>240000</v>
+        <v>470400</v>
       </c>
       <c r="E11" t="n">
-        <v>33.25</v>
+        <v>1.76</v>
       </c>
       <c r="F11" t="n">
-        <v>249375</v>
+        <v>184800</v>
       </c>
       <c r="G11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H11" t="n">
-        <v>6.88</v>
+        <v>2.48</v>
       </c>
       <c r="I11" t="n">
-        <v>6.62</v>
+        <v>6.32</v>
       </c>
       <c r="J11" t="n">
         <v>10</v>
       </c>
       <c r="K11" t="n">
-        <v>16500</v>
+        <v>11676</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SENA</t>
+          <t>CPNREIT</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>105000</v>
+        <v>55000</v>
       </c>
       <c r="C12" t="n">
-        <v>4.48</v>
+        <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>470400</v>
+        <v>990000</v>
       </c>
       <c r="E12" t="n">
-        <v>1.95</v>
+        <v>11</v>
       </c>
       <c r="F12" t="n">
-        <v>204750</v>
+        <v>605000</v>
       </c>
       <c r="G12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>2.48</v>
+        <v>3.58</v>
       </c>
       <c r="I12" t="n">
-        <v>5.7</v>
+        <v>5.86</v>
       </c>
       <c r="J12" t="n">
         <v>11</v>
       </c>
       <c r="K12" t="n">
-        <v>11676</v>
+        <v>35442</v>
       </c>
     </row>
   </sheetData>
